--- a/Assets/Resources/Excel/Item.xlsx
+++ b/Assets/Resources/Excel/Item.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30224"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{425F39EC-202F-4284-9423-4BEE86018913}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B7DEA6ED-57EA-4265-AF2B-7C7A008124C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="43">
   <si>
     <t>itemTID</t>
   </si>
@@ -51,6 +51,9 @@
     <t>itemMultiple</t>
   </si>
   <si>
+    <t>itemGrade</t>
+  </si>
+  <si>
     <t>icon</t>
   </si>
   <si>
@@ -106,6 +109,9 @@
   </si>
   <si>
     <t>weapon</t>
+  </si>
+  <si>
+    <t>normal</t>
   </si>
   <si>
     <t>Image_101_testGun</t>
@@ -511,27 +517,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U5"/>
+  <dimension ref="A1:V5"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="2" width="10.75" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="29" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="25.375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.25" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.875" customWidth="1"/>
-    <col min="12" max="12" width="8.375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.75" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="16.875" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.5" customWidth="1"/>
+    <col min="7" max="7" width="25.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.875" customWidth="1"/>
+    <col min="13" max="13" width="8.375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.75" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.875" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="11.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21">
+    <row r="1" spans="1:22">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -595,31 +602,34 @@
       <c r="U1" t="s">
         <v>20</v>
       </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="2" spans="1:21">
+    <row r="2" spans="1:22">
       <c r="A2">
         <v>101</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G2">
+        <v>25</v>
+      </c>
+      <c r="G2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2">
         <v>0.5</v>
-      </c>
-      <c r="H2">
-        <v>10</v>
       </c>
       <c r="I2">
         <v>10</v>
@@ -627,112 +637,124 @@
       <c r="J2">
         <v>10</v>
       </c>
-      <c r="L2">
+      <c r="K2">
+        <v>10</v>
+      </c>
+      <c r="M2">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:21">
+    <row r="3" spans="1:22">
       <c r="A3">
         <v>301</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E3">
         <v>5</v>
       </c>
       <c r="F3" t="s">
-        <v>28</v>
-      </c>
-      <c r="M3" t="s">
-        <v>29</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
+        <v>25</v>
+      </c>
+      <c r="G3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N3" t="s">
+        <v>31</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
         <v>10</v>
       </c>
-      <c r="Q3" t="s">
-        <v>30</v>
-      </c>
       <c r="R3" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="S3" t="s">
+        <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:21">
+    <row r="4" spans="1:22">
       <c r="A4">
         <v>302</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E4">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>34</v>
-      </c>
-      <c r="M4" t="s">
-        <v>29</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
+        <v>25</v>
+      </c>
+      <c r="G4" t="s">
+        <v>36</v>
+      </c>
+      <c r="N4" t="s">
+        <v>31</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
         <v>5</v>
       </c>
-      <c r="Q4" t="s">
-        <v>30</v>
-      </c>
       <c r="R4" t="s">
-        <v>35</v>
+        <v>32</v>
+      </c>
+      <c r="S4" t="s">
+        <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:21">
+    <row r="5" spans="1:22">
       <c r="A5">
         <v>401</v>
       </c>
       <c r="B5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E5">
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>39</v>
-      </c>
-      <c r="S5" t="s">
-        <v>40</v>
-      </c>
-      <c r="T5">
+        <v>25</v>
+      </c>
+      <c r="G5" t="s">
+        <v>41</v>
+      </c>
+      <c r="T5" t="s">
+        <v>42</v>
+      </c>
+      <c r="U5">
         <v>0</v>
       </c>
-      <c r="U5">
+      <c r="V5">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Item.xlsx
+++ b/Assets/Resources/Excel/Item.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30224"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B7DEA6ED-57EA-4265-AF2B-7C7A008124C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHubProjects\UnityProject_LucidDiver\Assets\Resources\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AE3BDE0-26AB-47EA-A56C-C554BCC06709}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="46">
   <si>
     <t>itemTID</t>
   </si>
@@ -163,18 +168,37 @@
   </si>
   <si>
     <t>main</t>
+  </si>
+  <si>
+    <t>rare</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uncommon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>epic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -221,9 +245,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -261,7 +285,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -367,7 +391,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -509,7 +533,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -518,7 +542,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:V5"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="10.75" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="29" bestFit="1" customWidth="1"/>
@@ -538,7 +562,7 @@
     <col min="22" max="23" width="11.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -606,7 +630,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:22">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>101</v>
       </c>
@@ -623,7 +647,7 @@
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="G2" t="s">
         <v>26</v>
@@ -644,7 +668,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:22">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>301</v>
       </c>
@@ -685,7 +709,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:22">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>302</v>
       </c>
@@ -702,7 +726,7 @@
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="G4" t="s">
         <v>36</v>
@@ -726,7 +750,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:22">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>401</v>
       </c>
@@ -743,7 +767,7 @@
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="G5" t="s">
         <v>41</v>
@@ -759,6 +783,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Assets/Resources/Excel/Item.xlsx
+++ b/Assets/Resources/Excel/Item.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHubProjects\UnityProject_LucidDiver\Assets\Resources\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Woo_260126\UnityProject_LucidDiver\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AE3BDE0-26AB-47EA-A56C-C554BCC06709}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{622F18E1-3D01-45D5-A6EF-F26F7AF069A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2145" yWindow="1185" windowWidth="21480" windowHeight="13380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -140,9 +138,6 @@
     <t>self</t>
   </si>
   <si>
-    <t>health_recover_inst</t>
-  </si>
-  <si>
     <t>이상한 사탕</t>
   </si>
   <si>
@@ -150,9 +145,6 @@
   </si>
   <si>
     <t>Image_302_WeirdCandy</t>
-  </si>
-  <si>
-    <t>mana_recover_inst</t>
   </si>
   <si>
     <t>기억 조각</t>
@@ -179,6 +171,14 @@
   </si>
   <si>
     <t>epic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>healHP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>healMP</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -245,9 +245,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -285,7 +285,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -391,7 +391,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -533,7 +533,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -647,7 +647,7 @@
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G2" t="s">
         <v>26</v>
@@ -706,7 +706,7 @@
         <v>32</v>
       </c>
       <c r="S3" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
@@ -714,10 +714,10 @@
         <v>302</v>
       </c>
       <c r="B4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" t="s">
         <v>34</v>
-      </c>
-      <c r="C4" t="s">
-        <v>35</v>
       </c>
       <c r="D4" t="s">
         <v>29</v>
@@ -726,10 +726,10 @@
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N4" t="s">
         <v>31</v>
@@ -747,7 +747,7 @@
         <v>32</v>
       </c>
       <c r="S4" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.3">
@@ -755,25 +755,25 @@
         <v>401</v>
       </c>
       <c r="B5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" t="s">
         <v>38</v>
-      </c>
-      <c r="C5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D5" t="s">
-        <v>40</v>
       </c>
       <c r="E5">
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="T5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="U5">
         <v>0</v>
@@ -785,5 +785,6 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Assets/Resources/Excel/Item.xlsx
+++ b/Assets/Resources/Excel/Item.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Woo_260126\UnityProject_LucidDiver\Assets\Resources\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHubProjects\UnityProject_LucidDiver\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{622F18E1-3D01-45D5-A6EF-F26F7AF069A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC632C04-FC8A-4847-9E77-5C04F132300D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2145" yWindow="1185" windowWidth="21480" windowHeight="13380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="86">
   <si>
     <t>itemTID</t>
   </si>
@@ -162,23 +162,143 @@
     <t>main</t>
   </si>
   <si>
+    <t>굳어버린 구급 봉투</t>
+  </si>
+  <si>
+    <t>artifact</t>
+  </si>
+  <si>
+    <t>UI_Icon_Normal_FirstAidPouch</t>
+  </si>
+  <si>
+    <t>itemFlavorText</t>
+  </si>
+  <si>
+    <t>artifactCategory</t>
+  </si>
+  <si>
+    <t>equipEffectType_0</t>
+  </si>
+  <si>
+    <t>equipEffectValue_0</t>
+  </si>
+  <si>
+    <t>equipEffectType_1</t>
+  </si>
+  <si>
+    <t>equipEffectValue_1</t>
+  </si>
+  <si>
+    <t>sellValue</t>
+  </si>
+  <si>
+    <t>개봉한 흔적은 없는데 내용물이 이미 굳어 있다. 손에 닿으면 차갑다.</t>
+  </si>
+  <si>
+    <t>HP_Related</t>
+  </si>
+  <si>
+    <t>hpRegen</t>
+  </si>
+  <si>
+    <t>역류하는 자양강장제</t>
+  </si>
+  <si>
+    <t>uncommon</t>
+  </si>
+  <si>
+    <t>UI_Icon_Uncommon_EnergyDrink</t>
+  </si>
+  <si>
+    <t>마트 음료 코너에서 발견한 강장제. 캔 안에서 액체가 위를 향해 흐른다. 마셔보면 달다.</t>
+  </si>
+  <si>
+    <t>MP_Related</t>
+  </si>
+  <si>
+    <t>mpRegen</t>
+  </si>
+  <si>
+    <t>구르지 않는 카트 바퀴</t>
+  </si>
+  <si>
     <t>rare</t>
+  </si>
+  <si>
+    <t>UI_Icon_Rare_CartWheel</t>
+  </si>
+  <si>
+    <t>침몽도시를 돌아다니던 카트에서 뜯어낸 바퀴. 닳아야 할 만큼 굴렀을 텐데 흠집 하나 없다. 손으로 쥐면 발이 가벼워진다.</t>
+  </si>
+  <si>
+    <t>Mobility</t>
+  </si>
+  <si>
+    <t>moveSpeedUp</t>
+  </si>
+  <si>
+    <t>지연된 시계 태엽</t>
+  </si>
+  <si>
+    <t>epic</t>
+  </si>
+  <si>
+    <t>UI_Icon_Epic_FrozenClockwork</t>
+  </si>
+  <si>
+    <t>침몽도시에서 시간은 흐르지 않고 소모된다. 이 태엽은 그 소모를 잠시 늦춘다.</t>
+  </si>
+  <si>
+    <t>TimeLimit</t>
+  </si>
+  <si>
+    <t>timeLimitSpeed</t>
+  </si>
+  <si>
+    <t>침식된 보안 경광봉</t>
+  </si>
+  <si>
+    <t>legend</t>
+  </si>
+  <si>
+    <t>UI_Icon_Legend_SecurityBaton</t>
+  </si>
+  <si>
+    <t>마트 경비원이 오래 찼던 경광봉. 침몽도시의 기운이 배어 손에 쥐면 묵직한 진동이 온다.</t>
+  </si>
+  <si>
+    <t>Combat</t>
+  </si>
+  <si>
+    <t>fireSpeedUp</t>
+  </si>
+  <si>
+    <t>fireMPDown</t>
+  </si>
+  <si>
+    <t>healHP</t>
+  </si>
+  <si>
+    <t>healMP</t>
+  </si>
+  <si>
+    <t>장착 중 HP가 초당 2.0씩 자연 회복된다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>uncommon</t>
+    <t>장착 중 MP가 초당 5.0씩 자연 회복된다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>epic</t>
+    <t>장착 중 이동 속도가 30% 증가한다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>healHP</t>
+    <t>장착 중 세션 시간 제한의 감소 속도가 40% 느려진다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>healMP</t>
+    <t>장착 중 공격 속도가 50% 증가하고, 기본 공격 시 소비되는 MP가 30% 감소한다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -222,11 +342,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -245,9 +362,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -285,7 +402,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -391,7 +508,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -533,7 +650,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -541,7 +658,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V5"/>
+  <dimension ref="A1:AC16"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="10.75" bestFit="1" customWidth="1"/>
@@ -559,10 +676,13 @@
     <col min="14" max="14" width="7.75" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="9.125" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="16.875" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="31.125" customWidth="1"/>
+    <col min="24" max="24" width="15.625" customWidth="1"/>
+    <col min="26" max="26" width="16.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -629,8 +749,29 @@
       <c r="V1" t="s">
         <v>21</v>
       </c>
+      <c r="W1" t="s">
+        <v>44</v>
+      </c>
+      <c r="X1" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>50</v>
+      </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>101</v>
       </c>
@@ -640,14 +781,14 @@
       <c r="C2" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" t="s">
         <v>24</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="G2" t="s">
         <v>26</v>
@@ -668,7 +809,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>301</v>
       </c>
@@ -706,10 +847,10 @@
         <v>32</v>
       </c>
       <c r="S3" t="s">
-        <v>44</v>
+        <v>79</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>302</v>
       </c>
@@ -726,7 +867,7 @@
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="G4" t="s">
         <v>35</v>
@@ -747,10 +888,10 @@
         <v>32</v>
       </c>
       <c r="S4" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>401</v>
       </c>
@@ -767,7 +908,7 @@
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="G5" t="s">
         <v>39</v>
@@ -782,6 +923,205 @@
         <v>0</v>
       </c>
     </row>
+    <row r="6" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>1001</v>
+      </c>
+      <c r="B6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" t="s">
+        <v>81</v>
+      </c>
+      <c r="D6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" t="s">
+        <v>43</v>
+      </c>
+      <c r="W6" t="s">
+        <v>51</v>
+      </c>
+      <c r="X6" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z6">
+        <v>2</v>
+      </c>
+      <c r="AC6">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="7" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>1002</v>
+      </c>
+      <c r="B7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7" t="s">
+        <v>55</v>
+      </c>
+      <c r="G7" t="s">
+        <v>56</v>
+      </c>
+      <c r="W7" t="s">
+        <v>57</v>
+      </c>
+      <c r="X7" t="s">
+        <v>58</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>59</v>
+      </c>
+      <c r="Z7">
+        <v>5</v>
+      </c>
+      <c r="AC7">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>1003</v>
+      </c>
+      <c r="B8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C8" t="s">
+        <v>83</v>
+      </c>
+      <c r="D8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8" t="s">
+        <v>61</v>
+      </c>
+      <c r="G8" t="s">
+        <v>62</v>
+      </c>
+      <c r="W8" t="s">
+        <v>63</v>
+      </c>
+      <c r="X8" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z8">
+        <v>0.3</v>
+      </c>
+      <c r="AC8">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>1004</v>
+      </c>
+      <c r="B9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C9" t="s">
+        <v>84</v>
+      </c>
+      <c r="D9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9" t="s">
+        <v>67</v>
+      </c>
+      <c r="G9" t="s">
+        <v>68</v>
+      </c>
+      <c r="W9" t="s">
+        <v>69</v>
+      </c>
+      <c r="X9" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>71</v>
+      </c>
+      <c r="Z9">
+        <v>0.6</v>
+      </c>
+      <c r="AC9">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>1005</v>
+      </c>
+      <c r="B10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10" t="s">
+        <v>85</v>
+      </c>
+      <c r="D10" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10" t="s">
+        <v>73</v>
+      </c>
+      <c r="G10" t="s">
+        <v>74</v>
+      </c>
+      <c r="W10" t="s">
+        <v>75</v>
+      </c>
+      <c r="X10" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z10">
+        <v>0.5</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>78</v>
+      </c>
+      <c r="AB10">
+        <v>0.3</v>
+      </c>
+      <c r="AC10">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:29" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="1:29" ht="17.25" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/Resources/Excel/Item.xlsx
+++ b/Assets/Resources/Excel/Item.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30306"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHubProjects\UnityProject_LucidDiver\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC632C04-FC8A-4847-9E77-5C04F132300D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8535FB98-9470-472B-AF70-BE2B7CB22DF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,6 +27,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -37,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="89">
   <si>
     <t>itemTID</t>
   </si>
@@ -105,6 +107,27 @@
     <t>linkRateGain</t>
   </si>
   <si>
+    <t>itemFlavorText</t>
+  </si>
+  <si>
+    <t>artifactCategory</t>
+  </si>
+  <si>
+    <t>equipEffectType_0</t>
+  </si>
+  <si>
+    <t>equipEffectValue_0</t>
+  </si>
+  <si>
+    <t>equipEffectType_1</t>
+  </si>
+  <si>
+    <t>equipEffectValue_1</t>
+  </si>
+  <si>
+    <t>sellValue</t>
+  </si>
+  <si>
     <t>에너지 권총</t>
   </si>
   <si>
@@ -114,21 +137,24 @@
     <t>weapon</t>
   </si>
   <si>
+    <t>rare</t>
+  </si>
+  <si>
+    <t>Image_101_testGun</t>
+  </si>
+  <si>
+    <t>변질된 붕대</t>
+  </si>
+  <si>
+    <t>섭취 시 캐릭터의 체력을 5 회복한다.</t>
+  </si>
+  <si>
+    <t>consume</t>
+  </si>
+  <si>
     <t>normal</t>
   </si>
   <si>
-    <t>Image_101_testGun</t>
-  </si>
-  <si>
-    <t>회복약</t>
-  </si>
-  <si>
-    <t>체력을 10 회복</t>
-  </si>
-  <si>
-    <t>consume</t>
-  </si>
-  <si>
     <t>Image_301_HealMedicine</t>
   </si>
   <si>
@@ -138,175 +164,160 @@
     <t>self</t>
   </si>
   <si>
+    <t>healHP</t>
+  </si>
+  <si>
+    <t>평범한 붕대가 아닌 것 같지만, 쓸 수 있을 것 같다.</t>
+  </si>
+  <si>
     <t>이상한 사탕</t>
   </si>
   <si>
-    <t>섭취 시 마나 5 회복</t>
+    <t>섭취 시 캐릭터의 마나를 5 회복한다.</t>
+  </si>
+  <si>
+    <t>uncommon</t>
   </si>
   <si>
     <t>Image_302_WeirdCandy</t>
   </si>
   <si>
+    <t>healMP</t>
+  </si>
+  <si>
+    <t>이상한 기운이 감도는 사탕. 맛있다.</t>
+  </si>
+  <si>
     <t>기억 조각</t>
   </si>
   <si>
-    <t>다이버의 동조율을 상승시킴</t>
+    <t>다이버의 동조율을 상승시킨다.</t>
   </si>
   <si>
     <t>memory</t>
   </si>
   <si>
+    <t>epic</t>
+  </si>
+  <si>
     <t>Image_401_MemoryPiece</t>
   </si>
   <si>
     <t>main</t>
   </si>
   <si>
+    <t>도시에서 주은 무언가의 조각. 이걸 들고 도시 밖으로 나간다면...</t>
+  </si>
+  <si>
     <t>굳어버린 구급 봉투</t>
-  </si>
-  <si>
-    <t>artifact</t>
-  </si>
-  <si>
-    <t>UI_Icon_Normal_FirstAidPouch</t>
-  </si>
-  <si>
-    <t>itemFlavorText</t>
-  </si>
-  <si>
-    <t>artifactCategory</t>
-  </si>
-  <si>
-    <t>equipEffectType_0</t>
-  </si>
-  <si>
-    <t>equipEffectValue_0</t>
-  </si>
-  <si>
-    <t>equipEffectType_1</t>
-  </si>
-  <si>
-    <t>equipEffectValue_1</t>
-  </si>
-  <si>
-    <t>sellValue</t>
-  </si>
-  <si>
-    <t>개봉한 흔적은 없는데 내용물이 이미 굳어 있다. 손에 닿으면 차갑다.</t>
-  </si>
-  <si>
-    <t>HP_Related</t>
-  </si>
-  <si>
-    <t>hpRegen</t>
-  </si>
-  <si>
-    <t>역류하는 자양강장제</t>
-  </si>
-  <si>
-    <t>uncommon</t>
-  </si>
-  <si>
-    <t>UI_Icon_Uncommon_EnergyDrink</t>
-  </si>
-  <si>
-    <t>마트 음료 코너에서 발견한 강장제. 캔 안에서 액체가 위를 향해 흐른다. 마셔보면 달다.</t>
-  </si>
-  <si>
-    <t>MP_Related</t>
-  </si>
-  <si>
-    <t>mpRegen</t>
-  </si>
-  <si>
-    <t>구르지 않는 카트 바퀴</t>
-  </si>
-  <si>
-    <t>rare</t>
-  </si>
-  <si>
-    <t>UI_Icon_Rare_CartWheel</t>
-  </si>
-  <si>
-    <t>침몽도시를 돌아다니던 카트에서 뜯어낸 바퀴. 닳아야 할 만큼 굴렀을 텐데 흠집 하나 없다. 손으로 쥐면 발이 가벼워진다.</t>
-  </si>
-  <si>
-    <t>Mobility</t>
-  </si>
-  <si>
-    <t>moveSpeedUp</t>
-  </si>
-  <si>
-    <t>지연된 시계 태엽</t>
-  </si>
-  <si>
-    <t>epic</t>
-  </si>
-  <si>
-    <t>UI_Icon_Epic_FrozenClockwork</t>
-  </si>
-  <si>
-    <t>침몽도시에서 시간은 흐르지 않고 소모된다. 이 태엽은 그 소모를 잠시 늦춘다.</t>
-  </si>
-  <si>
-    <t>TimeLimit</t>
-  </si>
-  <si>
-    <t>timeLimitSpeed</t>
-  </si>
-  <si>
-    <t>침식된 보안 경광봉</t>
-  </si>
-  <si>
-    <t>legend</t>
-  </si>
-  <si>
-    <t>UI_Icon_Legend_SecurityBaton</t>
-  </si>
-  <si>
-    <t>마트 경비원이 오래 찼던 경광봉. 침몽도시의 기운이 배어 손에 쥐면 묵직한 진동이 온다.</t>
-  </si>
-  <si>
-    <t>Combat</t>
-  </si>
-  <si>
-    <t>fireSpeedUp</t>
-  </si>
-  <si>
-    <t>fireMPDown</t>
-  </si>
-  <si>
-    <t>healHP</t>
-  </si>
-  <si>
-    <t>healMP</t>
   </si>
   <si>
     <t>장착 중 HP가 초당 2.0씩 자연 회복된다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>artifact</t>
+  </si>
+  <si>
+    <t>UI_Icon_Normal_FirstAidPouch</t>
+  </si>
+  <si>
+    <t>개봉한 흔적은 없는데 내용물이 이미 굳어 있다. 손에 닿으면 차갑다.</t>
+  </si>
+  <si>
+    <t>HP_Related</t>
+  </si>
+  <si>
+    <t>hpRegen</t>
+  </si>
+  <si>
+    <t>역류하는 자양강장제</t>
+  </si>
+  <si>
     <t>장착 중 MP가 초당 5.0씩 자연 회복된다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>UI_Icon_Uncommon_EnergyDrink</t>
+  </si>
+  <si>
+    <t>마트 음료 코너에서 발견한 강장제. 캔 안에서 액체가 위를 향해 흐른다. 마셔보면 달다.</t>
+  </si>
+  <si>
+    <t>MP_Related</t>
+  </si>
+  <si>
+    <t>mpRegen</t>
+  </si>
+  <si>
+    <t>구르지 않는 카트 바퀴</t>
+  </si>
+  <si>
     <t>장착 중 이동 속도가 30% 증가한다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>UI_Icon_Rare_CartWheel</t>
+  </si>
+  <si>
+    <t>침몽도시를 돌아다니던 카트에서 뜯어낸 바퀴. 닳아야 할 만큼 굴렀을 텐데 흠집 하나 없다. 손으로 쥐면 발이 가벼워진다.</t>
+  </si>
+  <si>
+    <t>Mobility</t>
+  </si>
+  <si>
+    <t>moveSpeedUp</t>
+  </si>
+  <si>
+    <t>지연된 시계 태엽</t>
+  </si>
+  <si>
     <t>장착 중 세션 시간 제한의 감소 속도가 40% 느려진다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>UI_Icon_Epic_FrozenClockwork</t>
+  </si>
+  <si>
+    <t>침몽도시에서 시간은 흐르지 않고 소모된다. 이 태엽은 그 소모를 잠시 늦춘다.</t>
+  </si>
+  <si>
+    <t>TimeLimit</t>
+  </si>
+  <si>
+    <t>timeLimitSpeed</t>
+  </si>
+  <si>
+    <t>침식된 보안 경광봉</t>
+  </si>
+  <si>
     <t>장착 중 공격 속도가 50% 증가하고, 기본 공격 시 소비되는 MP가 30% 감소한다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>legend</t>
+  </si>
+  <si>
+    <t>UI_Icon_Legend_SecurityBaton</t>
+  </si>
+  <si>
+    <t>마트 경비원이 오래 찼던 경광봉. 침몽도시의 기운이 배어 손에 쥐면 묵직한 진동이 온다.</t>
+  </si>
+  <si>
+    <t>Combat</t>
+  </si>
+  <si>
+    <t>fireSpeedUp</t>
+  </si>
+  <si>
+    <t>fireMPDown</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -342,8 +353,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -362,9 +376,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -402,7 +416,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -508,7 +522,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -650,7 +664,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -659,10 +673,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AC16"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="2" max="2" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.5" customWidth="1"/>
@@ -671,18 +685,18 @@
     <col min="9" max="9" width="9.125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8.25" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="21.125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.875" customWidth="1"/>
+    <col min="12" max="12" width="6.5" customWidth="1"/>
     <col min="13" max="13" width="8.375" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="7.75" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="9.125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.5" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="11.25" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="31.125" customWidth="1"/>
     <col min="24" max="24" width="15.625" customWidth="1"/>
     <col min="26" max="26" width="16.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:29">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -750,48 +764,48 @@
         <v>21</v>
       </c>
       <c r="W1" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="X1" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="Y1" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="Z1" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="AA1" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="AB1" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="AC1" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:29">
       <c r="A2">
         <v>101</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="G2" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="H2">
         <v>0.5</v>
@@ -809,30 +823,30 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:29" ht="33">
       <c r="A3">
         <v>301</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D3" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="E3">
         <v>5</v>
       </c>
       <c r="F3" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="G3" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="N3" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="O3">
         <v>0</v>
@@ -844,36 +858,39 @@
         <v>10</v>
       </c>
       <c r="R3" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="S3" t="s">
-        <v>79</v>
+        <v>41</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:29">
       <c r="A4">
         <v>302</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="E4">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="G4" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="N4" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="O4">
         <v>0</v>
@@ -885,36 +902,39 @@
         <v>5</v>
       </c>
       <c r="R4" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="S4" t="s">
-        <v>80</v>
+        <v>47</v>
+      </c>
+      <c r="W4" t="s">
+        <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:29" ht="33">
       <c r="A5">
         <v>401</v>
       </c>
       <c r="B5" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D5" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="E5">
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="G5" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="T5" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="U5">
         <v>0</v>
@@ -922,37 +942,40 @@
       <c r="V5">
         <v>0</v>
       </c>
+      <c r="W5" s="1" t="s">
+        <v>55</v>
+      </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:29">
       <c r="A6">
         <v>1001</v>
       </c>
       <c r="B6" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="C6" t="s">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="D6" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="G6" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="W6" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="X6" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="Y6" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="Z6">
         <v>2</v>
@@ -961,36 +984,36 @@
         <v>500</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:29">
       <c r="A7">
         <v>1002</v>
       </c>
       <c r="B7" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="E7">
         <v>1</v>
       </c>
       <c r="F7" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="G7" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="W7" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="X7" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="Y7" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="Z7">
         <v>5</v>
@@ -999,36 +1022,36 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="8" spans="1:29" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:29" ht="16.5" customHeight="1">
       <c r="A8">
         <v>1003</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="E8">
         <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="G8" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="W8" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="X8" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="Y8" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="Z8">
         <v>0.3</v>
@@ -1037,36 +1060,36 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:29">
       <c r="A9">
         <v>1004</v>
       </c>
       <c r="B9" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D9" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="E9">
         <v>1</v>
       </c>
       <c r="F9" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="G9" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="W9" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="X9" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="Y9" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="Z9">
         <v>0.6</v>
@@ -1075,42 +1098,42 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="10" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:29" ht="19.5" customHeight="1">
       <c r="A10">
         <v>1005</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="C10" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D10" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="E10">
         <v>1</v>
       </c>
       <c r="F10" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="G10" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="W10" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="X10" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="Y10" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="Z10">
         <v>0.5</v>
       </c>
       <c r="AA10" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AB10">
         <v>0.3</v>
@@ -1119,9 +1142,9 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:29" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="16" spans="1:29" ht="17.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="12" spans="1:29" ht="15" customHeight="1"/>
+    <row r="14" spans="1:29" ht="18.75" customHeight="1"/>
+    <row r="16" spans="1:29" ht="17.25" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
